--- a/TYPE-C_4K_TRANSMITTER/Design-Files/BOM/Client-BOM-TYPEC_4KTransmitter-v1.0.xlsx
+++ b/TYPE-C_4K_TRANSMITTER/Design-Files/BOM/Client-BOM-TYPEC_4KTransmitter-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="654">
   <si>
     <t>Component list</t>
   </si>
@@ -1437,9 +1437,6 @@
     <t>C105871</t>
   </si>
   <si>
-    <t>C100044</t>
-  </si>
-  <si>
     <t>C105578</t>
   </si>
   <si>
@@ -1461,9 +1458,6 @@
     <t>C499918</t>
   </si>
   <si>
-    <t>C5310990</t>
-  </si>
-  <si>
     <t>C178249</t>
   </si>
   <si>
@@ -1717,6 +1711,276 @@
   </si>
   <si>
     <t>Fuse</t>
+  </si>
+  <si>
+    <t>0.0027</t>
+  </si>
+  <si>
+    <t>0.0241</t>
+  </si>
+  <si>
+    <t>0.0011</t>
+  </si>
+  <si>
+    <t>0.0175</t>
+  </si>
+  <si>
+    <t>0.0020</t>
+  </si>
+  <si>
+    <t>0.1183</t>
+  </si>
+  <si>
+    <t>0.0533</t>
+  </si>
+  <si>
+    <t>0.0010</t>
+  </si>
+  <si>
+    <t>0.0026</t>
+  </si>
+  <si>
+    <t>0.0229</t>
+  </si>
+  <si>
+    <t>0.0075</t>
+  </si>
+  <si>
+    <t>0.0274</t>
+  </si>
+  <si>
+    <t>0.0285</t>
+  </si>
+  <si>
+    <t>0.2666</t>
+  </si>
+  <si>
+    <t>0.2428</t>
+  </si>
+  <si>
+    <t>0.0048</t>
+  </si>
+  <si>
+    <t>0.0062</t>
+  </si>
+  <si>
+    <t>0.0006</t>
+  </si>
+  <si>
+    <t>0.0045</t>
+  </si>
+  <si>
+    <t>0.0165</t>
+  </si>
+  <si>
+    <t>0.0082</t>
+  </si>
+  <si>
+    <t>0.0049</t>
+  </si>
+  <si>
+    <t>0.0021</t>
+  </si>
+  <si>
+    <t>0.0222</t>
+  </si>
+  <si>
+    <t>0.0013</t>
+  </si>
+  <si>
+    <t>0.0091</t>
+  </si>
+  <si>
+    <t>0.0223</t>
+  </si>
+  <si>
+    <t>0.0531</t>
+  </si>
+  <si>
+    <t>0.0399</t>
+  </si>
+  <si>
+    <t>0.0704</t>
+  </si>
+  <si>
+    <t>0.0352</t>
+  </si>
+  <si>
+    <t>0.0426</t>
+  </si>
+  <si>
+    <t>0.2243</t>
+  </si>
+  <si>
+    <t>1.1563</t>
+  </si>
+  <si>
+    <t>1.0757</t>
+  </si>
+  <si>
+    <t>0.0752</t>
+  </si>
+  <si>
+    <t>0.0571</t>
+  </si>
+  <si>
+    <t>0.0825</t>
+  </si>
+  <si>
+    <t>0.0188</t>
+  </si>
+  <si>
+    <t>0.1167</t>
+  </si>
+  <si>
+    <t>0.1743</t>
+  </si>
+  <si>
+    <t>0.3521</t>
+  </si>
+  <si>
+    <t>0.0348</t>
+  </si>
+  <si>
+    <t>0.0324</t>
+  </si>
+  <si>
+    <t>0.0137</t>
+  </si>
+  <si>
+    <t>0.0007</t>
+  </si>
+  <si>
+    <t>0.0005</t>
+  </si>
+  <si>
+    <t>0.0228</t>
+  </si>
+  <si>
+    <t>0.0192</t>
+  </si>
+  <si>
+    <t>0.0209</t>
+  </si>
+  <si>
+    <t>0.0100</t>
+  </si>
+  <si>
+    <t>0.0033</t>
+  </si>
+  <si>
+    <t>0.0009</t>
+  </si>
+  <si>
+    <t>0.0038</t>
+  </si>
+  <si>
+    <t>0.0237</t>
+  </si>
+  <si>
+    <t>0.0194</t>
+  </si>
+  <si>
+    <t>0.0202</t>
+  </si>
+  <si>
+    <t>0.1517</t>
+  </si>
+  <si>
+    <t>10.8677</t>
+  </si>
+  <si>
+    <t>0.9132</t>
+  </si>
+  <si>
+    <t>3.5626</t>
+  </si>
+  <si>
+    <t>0.4712</t>
+  </si>
+  <si>
+    <t>1.7255</t>
+  </si>
+  <si>
+    <t>2.9777</t>
+  </si>
+  <si>
+    <t>0.0705</t>
+  </si>
+  <si>
+    <t>0.1554</t>
+  </si>
+  <si>
+    <t>19.4080</t>
+  </si>
+  <si>
+    <t>0.5949</t>
+  </si>
+  <si>
+    <t>0.0385</t>
+  </si>
+  <si>
+    <t>13.9600</t>
+  </si>
+  <si>
+    <t>0.2306</t>
+  </si>
+  <si>
+    <t>0.0595</t>
+  </si>
+  <si>
+    <t>0.1993</t>
+  </si>
+  <si>
+    <t>0.3090</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>C106208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO NOT PLACE </t>
+  </si>
+  <si>
+    <t>C116699</t>
+  </si>
+  <si>
+    <t>----</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>C114755</t>
+  </si>
+  <si>
+    <t>C138008</t>
   </si>
 </sst>
 </file>
@@ -1728,7 +1992,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1878,6 +2142,40 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2081,7 +2379,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2189,6 +2487,15 @@
     <xf numFmtId="11" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2200,14 +2507,32 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2505,17 +2830,17 @@
     <col min="4" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2530,14 +2855,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -2548,7 +2873,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2572,7 +2897,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -2671,34 +2996,34 @@
         <v>365</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>399</v>
       </c>
       <c r="K7" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="N7" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="P7" s="43" t="s">
         <v>553</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="P7" s="46" t="s">
+      <c r="R7" s="12" t="s">
         <v>555</v>
-      </c>
-      <c r="Q7" s="12" t="s">
-        <v>556</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2725,14 +3050,14 @@
       <c r="H8" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>561</v>
+      <c r="I8" s="56" t="s">
+        <v>650</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L8" s="14">
         <v>2</v>
@@ -2744,10 +3069,10 @@
       <c r="N8" s="14">
         <v>11</v>
       </c>
-      <c r="O8" s="47" t="s">
-        <v>560</v>
-      </c>
-      <c r="P8" s="48">
+      <c r="O8" s="44" t="s">
+        <v>558</v>
+      </c>
+      <c r="P8" s="45">
         <v>2.1</v>
       </c>
       <c r="Q8" s="15">
@@ -2780,12 +3105,14 @@
       <c r="H9" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I9" s="20"/>
+      <c r="I9" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J9" s="20" t="s">
         <v>400</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L9" s="20">
         <v>2</v>
@@ -2794,12 +3121,18 @@
         <f t="shared" ref="M9" si="1">L9*5</f>
         <v>10</v>
       </c>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="21"/>
+      <c r="N9" s="20">
+        <v>100</v>
+      </c>
+      <c r="O9" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P9" s="45" t="s">
+        <v>564</v>
+      </c>
       <c r="Q9" s="21">
         <f t="shared" ref="Q9" si="2">P9*N9</f>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="R9" s="20"/>
     </row>
@@ -2827,12 +3160,14 @@
       <c r="H10" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I10" s="14"/>
+      <c r="I10" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J10" s="14" t="s">
         <v>401</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L10" s="14">
         <v>1</v>
@@ -2841,12 +3176,18 @@
         <f>L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="15"/>
+      <c r="N10" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P10" s="45" t="s">
+        <v>565</v>
+      </c>
       <c r="Q10" s="15">
         <f>P10*N10</f>
-        <v>0</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="R10" s="14"/>
     </row>
@@ -2874,12 +3215,14 @@
       <c r="H11" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I11" s="20"/>
+      <c r="I11" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J11" s="20" t="s">
         <v>402</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L11" s="20">
         <v>53</v>
@@ -2888,12 +3231,18 @@
         <f t="shared" ref="M11" si="3">L11*5</f>
         <v>265</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="21"/>
+      <c r="N11" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="O11" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P11" s="45" t="s">
+        <v>566</v>
+      </c>
       <c r="Q11" s="21">
         <f t="shared" ref="Q11" si="4">P11*N11</f>
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="R11" s="20"/>
     </row>
@@ -2921,12 +3270,14 @@
       <c r="H12" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I12" s="14"/>
+      <c r="I12" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J12" s="14" t="s">
         <v>403</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L12" s="14">
         <v>13</v>
@@ -2935,12 +3286,18 @@
         <f>L12*5</f>
         <v>65</v>
       </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="15"/>
+      <c r="N12" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O12" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P12" s="45" t="s">
+        <v>567</v>
+      </c>
       <c r="Q12" s="15">
         <f>P12*N12</f>
-        <v>0</v>
+        <v>1.7500000000000002</v>
       </c>
       <c r="R12" s="14"/>
     </row>
@@ -2968,12 +3325,14 @@
       <c r="H13" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="I13" s="20"/>
+      <c r="I13" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J13" s="20" t="s">
         <v>404</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L13" s="20">
         <v>2</v>
@@ -2982,12 +3341,18 @@
         <f t="shared" ref="M13" si="5">L13*5</f>
         <v>10</v>
       </c>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="21"/>
+      <c r="N13" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O13" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P13" s="45" t="s">
+        <v>568</v>
+      </c>
       <c r="Q13" s="21">
         <f t="shared" ref="Q13" si="6">P13*N13</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R13" s="20"/>
     </row>
@@ -3015,12 +3380,14 @@
       <c r="H14" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="I14" s="14"/>
+      <c r="I14" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J14" s="14" t="s">
         <v>405</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L14" s="14">
         <v>23</v>
@@ -3029,12 +3396,18 @@
         <f>L14*5</f>
         <v>115</v>
       </c>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="15"/>
+      <c r="N14" s="14">
+        <v>120</v>
+      </c>
+      <c r="O14" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P14" s="45" t="s">
+        <v>569</v>
+      </c>
       <c r="Q14" s="15">
         <f>P14*N14</f>
-        <v>0</v>
+        <v>14.196</v>
       </c>
       <c r="R14" s="14"/>
     </row>
@@ -3062,12 +3435,14 @@
       <c r="H15" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="I15" s="20"/>
+      <c r="I15" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J15" s="20" t="s">
         <v>406</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L15" s="20">
         <v>3</v>
@@ -3076,12 +3451,18 @@
         <f t="shared" ref="M15" si="7">L15*5</f>
         <v>15</v>
       </c>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="21"/>
+      <c r="N15" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="O15" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P15" s="45" t="s">
+        <v>570</v>
+      </c>
       <c r="Q15" s="21">
         <f t="shared" ref="Q15" si="8">P15*N15</f>
-        <v>0</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="R15" s="20"/>
     </row>
@@ -3109,12 +3490,14 @@
       <c r="H16" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I16" s="14"/>
+      <c r="I16" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J16" s="14" t="s">
         <v>407</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L16" s="14">
         <v>18</v>
@@ -3123,12 +3506,18 @@
         <f>L16*5</f>
         <v>90</v>
       </c>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="15"/>
+      <c r="N16" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O16" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P16" s="45" t="s">
+        <v>566</v>
+      </c>
       <c r="Q16" s="15">
         <f>P16*N16</f>
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="R16" s="14"/>
     </row>
@@ -3156,10 +3545,14 @@
       <c r="H17" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
+      <c r="I17" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>647</v>
+      </c>
       <c r="K17" s="20" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L17" s="20">
         <v>1</v>
@@ -3168,12 +3561,18 @@
         <f t="shared" ref="M17" si="9">L17*5</f>
         <v>5</v>
       </c>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="21"/>
+      <c r="N17" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O17" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P17" s="45" t="s">
+        <v>571</v>
+      </c>
       <c r="Q17" s="21">
         <f t="shared" ref="Q17" si="10">P17*N17</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R17" s="20"/>
     </row>
@@ -3201,12 +3600,14 @@
       <c r="H18" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I18" s="14"/>
+      <c r="I18" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J18" s="14" t="s">
         <v>408</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="L18" s="14">
         <v>39</v>
@@ -3215,12 +3616,18 @@
         <f>L18*5</f>
         <v>195</v>
       </c>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="15"/>
+      <c r="N18" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P18" s="45" t="s">
+        <v>572</v>
+      </c>
       <c r="Q18" s="15">
         <f>P18*N18</f>
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="R18" s="14"/>
     </row>
@@ -3248,12 +3655,14 @@
       <c r="H19" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="20"/>
+      <c r="I19" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J19" s="20" t="s">
         <v>409</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L19" s="20">
         <v>9</v>
@@ -3262,12 +3671,18 @@
         <f t="shared" ref="M19" si="11">L19*5</f>
         <v>45</v>
       </c>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="21"/>
+      <c r="N19" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O19" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P19" s="45" t="s">
+        <v>573</v>
+      </c>
       <c r="Q19" s="21">
         <f t="shared" ref="Q19" si="12">P19*N19</f>
-        <v>0</v>
+        <v>1.145</v>
       </c>
       <c r="R19" s="20"/>
     </row>
@@ -3295,12 +3710,14 @@
       <c r="H20" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="I20" s="14"/>
+      <c r="I20" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J20" s="14" t="s">
         <v>410</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L20" s="14">
         <v>19</v>
@@ -3309,12 +3726,18 @@
         <f>L20*5</f>
         <v>95</v>
       </c>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="15"/>
+      <c r="N20" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O20" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P20" s="45" t="s">
+        <v>574</v>
+      </c>
       <c r="Q20" s="15">
         <f>P20*N20</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R20" s="14"/>
     </row>
@@ -3342,12 +3765,14 @@
       <c r="H21" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I21" s="20"/>
+      <c r="I21" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J21" s="20" t="s">
         <v>411</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L21" s="20">
         <v>67</v>
@@ -3356,12 +3781,18 @@
         <f t="shared" ref="M21" si="13">L21*5</f>
         <v>335</v>
       </c>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="21"/>
+      <c r="N21" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="O21" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P21" s="45" t="s">
+        <v>566</v>
+      </c>
       <c r="Q21" s="21">
         <f t="shared" ref="Q21" si="14">P21*N21</f>
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="R21" s="20"/>
     </row>
@@ -3389,12 +3820,14 @@
       <c r="H22" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I22" s="14"/>
+      <c r="I22" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J22" s="14" t="s">
         <v>412</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="L22" s="14">
         <v>2</v>
@@ -3403,12 +3836,18 @@
         <f>L22*5</f>
         <v>10</v>
       </c>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="15"/>
+      <c r="N22" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O22" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P22" s="45" t="s">
+        <v>571</v>
+      </c>
       <c r="Q22" s="15">
         <f>P22*N22</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R22" s="14"/>
     </row>
@@ -3436,12 +3875,14 @@
       <c r="H23" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I23" s="20"/>
+      <c r="I23" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J23" s="20" t="s">
         <v>413</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L23" s="20">
         <v>3</v>
@@ -3450,12 +3891,18 @@
         <f t="shared" ref="M23" si="15">L23*5</f>
         <v>15</v>
       </c>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="21"/>
+      <c r="N23" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="O23" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P23" s="45" t="s">
+        <v>575</v>
+      </c>
       <c r="Q23" s="21">
         <f t="shared" ref="Q23" si="16">P23*N23</f>
-        <v>0</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="R23" s="20"/>
     </row>
@@ -3483,12 +3930,14 @@
       <c r="H24" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="I24" s="14"/>
+      <c r="I24" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J24" s="14" t="s">
         <v>414</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L24" s="14">
         <v>3</v>
@@ -3497,12 +3946,18 @@
         <f>L24*5</f>
         <v>15</v>
       </c>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="15"/>
+      <c r="N24" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O24" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P24" s="45" t="s">
+        <v>576</v>
+      </c>
       <c r="Q24" s="15">
         <f>P24*N24</f>
-        <v>0</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="R24" s="14"/>
     </row>
@@ -3530,12 +3985,14 @@
       <c r="H25" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I25" s="20"/>
+      <c r="I25" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J25" s="20" t="s">
         <v>402</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L25" s="20">
         <v>4</v>
@@ -3544,12 +4001,18 @@
         <f t="shared" ref="M25" si="17">L25*5</f>
         <v>20</v>
       </c>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="21"/>
+      <c r="N25" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O25" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P25" s="45" t="s">
+        <v>566</v>
+      </c>
       <c r="Q25" s="21">
         <f t="shared" ref="Q25" si="18">P25*N25</f>
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="R25" s="20"/>
     </row>
@@ -3577,12 +4040,14 @@
       <c r="H26" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="I26" s="14"/>
+      <c r="I26" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J26" s="14" t="s">
         <v>415</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L26" s="14">
         <v>1</v>
@@ -3591,12 +4056,18 @@
         <f>L26*5</f>
         <v>5</v>
       </c>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="15"/>
+      <c r="N26" s="14">
+        <v>10</v>
+      </c>
+      <c r="O26" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P26" s="45" t="s">
+        <v>577</v>
+      </c>
       <c r="Q26" s="15">
         <f>P26*N26</f>
-        <v>0</v>
+        <v>2.6659999999999999</v>
       </c>
       <c r="R26" s="14"/>
     </row>
@@ -3624,12 +4095,14 @@
       <c r="H27" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="I27" s="20"/>
+      <c r="I27" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J27" s="20" t="s">
         <v>416</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L27" s="20">
         <v>2</v>
@@ -3638,12 +4111,18 @@
         <f t="shared" ref="M27" si="19">L27*5</f>
         <v>10</v>
       </c>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="21"/>
+      <c r="N27" s="20">
+        <v>15</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P27" s="45" t="s">
+        <v>578</v>
+      </c>
       <c r="Q27" s="21">
         <f t="shared" ref="Q27" si="20">P27*N27</f>
-        <v>0</v>
+        <v>3.6419999999999999</v>
       </c>
       <c r="R27" s="20"/>
     </row>
@@ -3671,10 +4150,12 @@
       <c r="H28" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="I28" s="14"/>
+      <c r="I28" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J28" s="14"/>
       <c r="K28" s="14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L28" s="14">
         <v>2</v>
@@ -3683,12 +4164,18 @@
         <f>L28*5</f>
         <v>10</v>
       </c>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="15"/>
+      <c r="N28" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P28" s="45" t="s">
+        <v>579</v>
+      </c>
       <c r="Q28" s="15">
         <f>P28*N28</f>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R28" s="14"/>
     </row>
@@ -3716,12 +4203,14 @@
       <c r="H29" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I29" s="20"/>
+      <c r="I29" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J29" s="20" t="s">
         <v>417</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L29" s="20">
         <v>4</v>
@@ -3730,12 +4219,18 @@
         <f t="shared" ref="M29" si="21">L29*5</f>
         <v>20</v>
       </c>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="21"/>
+      <c r="N29" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O29" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P29" s="45" t="s">
+        <v>580</v>
+      </c>
       <c r="Q29" s="21">
         <f t="shared" ref="Q29" si="22">P29*N29</f>
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="R29" s="20"/>
     </row>
@@ -3763,12 +4258,14 @@
       <c r="H30" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="I30" s="14"/>
+      <c r="I30" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J30" s="14" t="s">
         <v>418</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L30" s="14">
         <v>4</v>
@@ -3777,12 +4274,18 @@
         <f>L30*5</f>
         <v>20</v>
       </c>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="15"/>
+      <c r="N30" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O30" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P30" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q30" s="15">
         <f>P30*N30</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="R30" s="14"/>
     </row>
@@ -3810,12 +4313,14 @@
       <c r="H31" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="I31" s="20"/>
+      <c r="I31" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J31" s="20" t="s">
         <v>419</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L31" s="20">
         <v>3</v>
@@ -3824,12 +4329,18 @@
         <f t="shared" ref="M31" si="23">L31*5</f>
         <v>15</v>
       </c>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="21"/>
+      <c r="N31" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O31" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P31" s="45" t="s">
+        <v>582</v>
+      </c>
       <c r="Q31" s="21">
         <f t="shared" ref="Q31" si="24">P31*N31</f>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="R31" s="20"/>
     </row>
@@ -3857,12 +4368,14 @@
       <c r="H32" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I32" s="14"/>
+      <c r="I32" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J32" s="14" t="s">
         <v>420</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L32" s="14">
         <v>1</v>
@@ -3871,12 +4384,18 @@
         <f>L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="15"/>
+      <c r="N32" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="O32" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P32" s="45" t="s">
+        <v>583</v>
+      </c>
       <c r="Q32" s="15">
         <f>P32*N32</f>
-        <v>0</v>
+        <v>0.82500000000000007</v>
       </c>
       <c r="R32" s="14"/>
     </row>
@@ -3889,43 +4408,52 @@
       <c r="C33" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="49" t="s">
         <v>238</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="49" t="s">
         <v>295</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H33" s="49" t="s">
         <v>367</v>
       </c>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20" t="s">
+      <c r="I33" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J33" s="49" t="s">
         <v>421</v>
       </c>
-      <c r="K33" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="L33" s="20">
+      <c r="K33" s="49" t="s">
+        <v>507</v>
+      </c>
+      <c r="L33" s="49">
         <v>4</v>
       </c>
-      <c r="M33" s="20">
+      <c r="M33" s="49">
         <f t="shared" ref="M33" si="25">L33*5</f>
         <v>20</v>
       </c>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21">
-        <f t="shared" ref="Q33" si="26">P33*N33</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="20"/>
+      <c r="N33" s="49" t="s">
+        <v>638</v>
+      </c>
+      <c r="O33" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P33" s="51" t="s">
+        <v>559</v>
+      </c>
+      <c r="Q33" s="52" t="s">
+        <v>559</v>
+      </c>
+      <c r="R33" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="1"/>
@@ -3951,12 +4479,14 @@
       <c r="H34" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="I34" s="14"/>
+      <c r="I34" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J34" s="14" t="s">
         <v>422</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L34" s="14">
         <v>6</v>
@@ -3965,12 +4495,18 @@
         <f>L34*5</f>
         <v>30</v>
       </c>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="15"/>
+      <c r="N34" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="O34" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P34" s="45" t="s">
+        <v>584</v>
+      </c>
       <c r="Q34" s="15">
         <f>P34*N34</f>
-        <v>0</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="R34" s="14"/>
     </row>
@@ -3983,43 +4519,53 @@
       <c r="C35" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="G35" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="H35" s="20" t="s">
+      <c r="H35" s="53" t="s">
         <v>368</v>
       </c>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20" t="s">
+      <c r="I35" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J35" s="53" t="s">
         <v>423</v>
       </c>
-      <c r="K35" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="L35" s="20">
+      <c r="K35" s="53" t="s">
+        <v>507</v>
+      </c>
+      <c r="L35" s="53">
         <v>1</v>
       </c>
-      <c r="M35" s="20">
-        <f t="shared" ref="M35" si="27">L35*5</f>
+      <c r="M35" s="53">
+        <f t="shared" ref="M35" si="26">L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21">
-        <f t="shared" ref="Q35" si="28">P35*N35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="20"/>
+      <c r="N35" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="O35" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P35" s="51" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q35" s="54">
+        <f t="shared" ref="Q35" si="27">P35*N35</f>
+        <v>0.49</v>
+      </c>
+      <c r="R35" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1"/>
@@ -4045,12 +4591,14 @@
       <c r="H36" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="I36" s="14"/>
+      <c r="I36" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J36" s="14" t="s">
         <v>424</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L36" s="14">
         <v>1</v>
@@ -4059,12 +4607,18 @@
         <f>L36*5</f>
         <v>5</v>
       </c>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="15"/>
+      <c r="N36" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O36" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P36" s="45" t="s">
+        <v>586</v>
+      </c>
       <c r="Q36" s="15">
         <f>P36*N36</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="R36" s="14"/>
     </row>
@@ -4092,26 +4646,34 @@
       <c r="H37" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="I37" s="20"/>
+      <c r="I37" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J37" s="20" t="s">
         <v>425</v>
       </c>
       <c r="K37" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L37" s="20">
         <v>2</v>
       </c>
       <c r="M37" s="20">
-        <f t="shared" ref="M37" si="29">L37*5</f>
+        <f t="shared" ref="M37" si="28">L37*5</f>
         <v>10</v>
       </c>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="21"/>
+      <c r="N37" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="O37" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P37" s="45" t="s">
+        <v>587</v>
+      </c>
       <c r="Q37" s="21">
-        <f t="shared" ref="Q37" si="30">P37*N37</f>
-        <v>0</v>
+        <f t="shared" ref="Q37" si="29">P37*N37</f>
+        <v>0.44400000000000001</v>
       </c>
       <c r="R37" s="20"/>
     </row>
@@ -4124,43 +4686,53 @@
       <c r="C38" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="53" t="s">
         <v>300</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14" t="s">
+      <c r="I38" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J38" s="53" t="s">
         <v>426</v>
       </c>
-      <c r="K38" s="14" t="s">
-        <v>512</v>
-      </c>
-      <c r="L38" s="14">
+      <c r="K38" s="53" t="s">
+        <v>510</v>
+      </c>
+      <c r="L38" s="53">
         <v>1</v>
       </c>
-      <c r="M38" s="14">
+      <c r="M38" s="53">
         <f>L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15">
+      <c r="N38" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="O38" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P38" s="51" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q38" s="54">
         <f>P38*N38</f>
-        <v>0</v>
-      </c>
-      <c r="R38" s="14"/>
+        <v>0.13</v>
+      </c>
+      <c r="R38" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="39" spans="1:18" ht="24">
       <c r="A39" s="1"/>
@@ -4178,7 +4750,7 @@
         <v>164</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G39" s="20" t="s">
         <v>301</v>
@@ -4186,26 +4758,34 @@
       <c r="H39" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="I39" s="20"/>
+      <c r="I39" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J39" s="20" t="s">
         <v>427</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L39" s="20">
         <v>7</v>
       </c>
       <c r="M39" s="20">
-        <f t="shared" ref="M39" si="31">L39*5</f>
+        <f t="shared" ref="M39" si="30">L39*5</f>
         <v>35</v>
       </c>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-      <c r="P39" s="21"/>
+      <c r="N39" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O39" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P39" s="45" t="s">
+        <v>589</v>
+      </c>
       <c r="Q39" s="21">
-        <f t="shared" ref="Q39" si="32">P39*N39</f>
-        <v>0</v>
+        <f t="shared" ref="Q39" si="31">P39*N39</f>
+        <v>0.45500000000000002</v>
       </c>
       <c r="R39" s="20"/>
     </row>
@@ -4233,12 +4813,14 @@
       <c r="H40" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="I40" s="14"/>
+      <c r="I40" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J40" s="14" t="s">
         <v>428</v>
       </c>
       <c r="K40" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L40" s="14">
         <v>2</v>
@@ -4247,12 +4829,18 @@
         <f>L40*5</f>
         <v>10</v>
       </c>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="15"/>
+      <c r="N40" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O40" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P40" s="45" t="s">
+        <v>590</v>
+      </c>
       <c r="Q40" s="15">
         <f>P40*N40</f>
-        <v>0</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="R40" s="14"/>
     </row>
@@ -4280,26 +4868,34 @@
       <c r="H41" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="I41" s="20"/>
+      <c r="I41" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J41" s="20" t="s">
         <v>429</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L41" s="20">
         <v>2</v>
       </c>
       <c r="M41" s="20">
-        <f t="shared" ref="M41" si="33">L41*5</f>
+        <f t="shared" ref="M41" si="32">L41*5</f>
         <v>10</v>
       </c>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="21"/>
+      <c r="N41" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="O41" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P41" s="45" t="s">
+        <v>591</v>
+      </c>
       <c r="Q41" s="21">
-        <f t="shared" ref="Q41" si="34">P41*N41</f>
-        <v>0</v>
+        <f t="shared" ref="Q41" si="33">P41*N41</f>
+        <v>0.53100000000000003</v>
       </c>
       <c r="R41" s="20"/>
     </row>
@@ -4327,12 +4923,14 @@
       <c r="H42" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="I42" s="14"/>
+      <c r="I42" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J42" s="14" t="s">
         <v>430</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L42" s="14">
         <v>3</v>
@@ -4341,12 +4939,18 @@
         <f>L42*5</f>
         <v>15</v>
       </c>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="15"/>
+      <c r="N42" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O42" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P42" s="45" t="s">
+        <v>592</v>
+      </c>
       <c r="Q42" s="15">
         <f>P42*N42</f>
-        <v>0</v>
+        <v>0.79799999999999993</v>
       </c>
       <c r="R42" s="14"/>
     </row>
@@ -4357,7 +4961,7 @@
         <v>36</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>63</v>
@@ -4374,26 +4978,34 @@
       <c r="H43" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="I43" s="20"/>
+      <c r="I43" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J43" s="20" t="s">
         <v>431</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L43" s="20">
         <v>1</v>
       </c>
       <c r="M43" s="20">
-        <f t="shared" ref="M43" si="35">L43*5</f>
+        <f t="shared" ref="M43" si="34">L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="21"/>
+      <c r="N43" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="O43" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P43" s="45" t="s">
+        <v>593</v>
+      </c>
       <c r="Q43" s="21">
-        <f t="shared" ref="Q43" si="36">P43*N43</f>
-        <v>0</v>
+        <f t="shared" ref="Q43" si="35">P43*N43</f>
+        <v>0.70400000000000007</v>
       </c>
       <c r="R43" s="20"/>
     </row>
@@ -4413,7 +5025,7 @@
         <v>169</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>306</v>
@@ -4421,12 +5033,14 @@
       <c r="H44" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="I44" s="14"/>
+      <c r="I44" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J44" s="14" t="s">
         <v>432</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L44" s="14">
         <v>6</v>
@@ -4435,12 +5049,18 @@
         <f>L44*5</f>
         <v>30</v>
       </c>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="15"/>
+      <c r="N44" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="O44" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P44" s="45" t="s">
+        <v>594</v>
+      </c>
       <c r="Q44" s="15">
         <f>P44*N44</f>
-        <v>0</v>
+        <v>1.4080000000000001</v>
       </c>
       <c r="R44" s="14"/>
     </row>
@@ -4468,26 +5088,34 @@
       <c r="H45" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="I45" s="20"/>
+      <c r="I45" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J45" s="20" t="s">
         <v>433</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L45" s="20">
         <v>1</v>
       </c>
       <c r="M45" s="20">
-        <f t="shared" ref="M45" si="37">L45*5</f>
+        <f t="shared" ref="M45" si="36">L45*5</f>
         <v>5</v>
       </c>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="21"/>
+      <c r="N45" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="O45" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P45" s="45" t="s">
+        <v>595</v>
+      </c>
       <c r="Q45" s="21">
-        <f t="shared" ref="Q45" si="38">P45*N45</f>
-        <v>0</v>
+        <f t="shared" ref="Q45" si="37">P45*N45</f>
+        <v>0.42599999999999999</v>
       </c>
       <c r="R45" s="20"/>
     </row>
@@ -4507,7 +5135,7 @@
         <v>171</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>308</v>
@@ -4515,12 +5143,14 @@
       <c r="H46" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="I46" s="14"/>
+      <c r="I46" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J46" s="14" t="s">
         <v>434</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L46" s="14">
         <v>1</v>
@@ -4529,12 +5159,18 @@
         <f>L46*5</f>
         <v>5</v>
       </c>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="15"/>
+      <c r="N46" s="14">
+        <v>10</v>
+      </c>
+      <c r="O46" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P46" s="45" t="s">
+        <v>596</v>
+      </c>
       <c r="Q46" s="15">
         <f>P46*N46</f>
-        <v>0</v>
+        <v>2.2429999999999999</v>
       </c>
       <c r="R46" s="14"/>
     </row>
@@ -4554,7 +5190,7 @@
         <v>172</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G47" s="20" t="s">
         <v>246</v>
@@ -4562,26 +5198,34 @@
       <c r="H47" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="I47" s="20"/>
+      <c r="I47" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J47" s="20" t="s">
         <v>435</v>
       </c>
       <c r="K47" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L47" s="20">
         <v>1</v>
       </c>
       <c r="M47" s="20">
-        <f t="shared" ref="M47" si="39">L47*5</f>
+        <f t="shared" ref="M47" si="38">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="20"/>
-      <c r="O47" s="20"/>
-      <c r="P47" s="21"/>
+      <c r="N47" s="20">
+        <v>6</v>
+      </c>
+      <c r="O47" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P47" s="45" t="s">
+        <v>597</v>
+      </c>
       <c r="Q47" s="21">
-        <f t="shared" ref="Q47" si="40">P47*N47</f>
-        <v>0</v>
+        <f t="shared" ref="Q47" si="39">P47*N47</f>
+        <v>6.9378000000000011</v>
       </c>
       <c r="R47" s="20"/>
     </row>
@@ -4601,7 +5245,7 @@
         <v>173</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G48" s="42" t="s">
         <v>247</v>
@@ -4609,12 +5253,14 @@
       <c r="H48" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="I48" s="14"/>
+      <c r="I48" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J48" s="14" t="s">
         <v>436</v>
       </c>
       <c r="K48" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L48" s="14">
         <v>1</v>
@@ -4623,12 +5269,18 @@
         <f>L48*5</f>
         <v>5</v>
       </c>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="15"/>
+      <c r="N48" s="14">
+        <v>6</v>
+      </c>
+      <c r="O48" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P48" s="45" t="s">
+        <v>598</v>
+      </c>
       <c r="Q48" s="15">
         <f>P48*N48</f>
-        <v>0</v>
+        <v>6.4542000000000002</v>
       </c>
       <c r="R48" s="14"/>
     </row>
@@ -4648,7 +5300,7 @@
         <v>174</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>248</v>
@@ -4656,26 +5308,34 @@
       <c r="H49" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="I49" s="20"/>
+      <c r="I49" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J49" s="20" t="s">
         <v>437</v>
       </c>
       <c r="K49" s="20" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L49" s="20">
         <v>2</v>
       </c>
       <c r="M49" s="20">
-        <f t="shared" ref="M49" si="41">L49*5</f>
+        <f t="shared" ref="M49" si="40">L49*5</f>
         <v>10</v>
       </c>
-      <c r="N49" s="20"/>
-      <c r="O49" s="20"/>
-      <c r="P49" s="21"/>
+      <c r="N49" s="20">
+        <v>20</v>
+      </c>
+      <c r="O49" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P49" s="45" t="s">
+        <v>599</v>
+      </c>
       <c r="Q49" s="21">
-        <f t="shared" ref="Q49" si="42">P49*N49</f>
-        <v>0</v>
+        <f t="shared" ref="Q49" si="41">P49*N49</f>
+        <v>1.504</v>
       </c>
       <c r="R49" s="20"/>
     </row>
@@ -4695,7 +5355,7 @@
         <v>175</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>309</v>
@@ -4703,12 +5363,14 @@
       <c r="H50" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="I50" s="14"/>
+      <c r="I50" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J50" s="14" t="s">
         <v>438</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="L50" s="14">
         <v>1</v>
@@ -4717,12 +5379,18 @@
         <f>L50*5</f>
         <v>5</v>
       </c>
-      <c r="N50" s="14"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="15"/>
+      <c r="N50" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="O50" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P50" s="45" t="s">
+        <v>600</v>
+      </c>
       <c r="Q50" s="15">
         <f>P50*N50</f>
-        <v>0</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="R50" s="14"/>
     </row>
@@ -4742,7 +5410,7 @@
         <v>176</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G51" s="20" t="s">
         <v>249</v>
@@ -4750,26 +5418,34 @@
       <c r="H51" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="I51" s="20"/>
+      <c r="I51" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J51" s="20" t="s">
         <v>439</v>
       </c>
       <c r="K51" s="20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="L51" s="20">
         <v>5</v>
       </c>
       <c r="M51" s="20">
-        <f t="shared" ref="M51" si="43">L51*5</f>
+        <f t="shared" ref="M51" si="42">L51*5</f>
         <v>25</v>
       </c>
-      <c r="N51" s="20"/>
-      <c r="O51" s="20"/>
-      <c r="P51" s="21"/>
+      <c r="N51" s="20">
+        <v>30</v>
+      </c>
+      <c r="O51" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P51" s="45" t="s">
+        <v>601</v>
+      </c>
       <c r="Q51" s="21">
-        <f t="shared" ref="Q51" si="44">P51*N51</f>
-        <v>0</v>
+        <f t="shared" ref="Q51" si="43">P51*N51</f>
+        <v>2.4750000000000001</v>
       </c>
       <c r="R51" s="20"/>
     </row>
@@ -4789,7 +5465,7 @@
         <v>177</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G52" s="14" t="s">
         <v>310</v>
@@ -4797,12 +5473,14 @@
       <c r="H52" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="I52" s="14"/>
+      <c r="I52" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J52" s="14" t="s">
         <v>440</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L52" s="14">
         <v>2</v>
@@ -4811,12 +5489,18 @@
         <f>L52*5</f>
         <v>10</v>
       </c>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="15"/>
+      <c r="N52" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O52" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P52" s="45" t="s">
+        <v>602</v>
+      </c>
       <c r="Q52" s="15">
         <f>P52*N52</f>
-        <v>0</v>
+        <v>0.376</v>
       </c>
       <c r="R52" s="14"/>
     </row>
@@ -4836,7 +5520,7 @@
         <v>178</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G53" s="20" t="s">
         <v>311</v>
@@ -4844,26 +5528,34 @@
       <c r="H53" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="I53" s="20"/>
+      <c r="I53" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J53" s="20" t="s">
         <v>441</v>
       </c>
       <c r="K53" s="20" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
       </c>
       <c r="M53" s="20">
-        <f t="shared" ref="M53" si="45">L53*5</f>
+        <f t="shared" ref="M53" si="44">L53*5</f>
         <v>5</v>
       </c>
-      <c r="N53" s="20"/>
-      <c r="O53" s="20"/>
-      <c r="P53" s="21"/>
+      <c r="N53" s="20">
+        <v>10</v>
+      </c>
+      <c r="O53" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P53" s="45" t="s">
+        <v>603</v>
+      </c>
       <c r="Q53" s="21">
-        <f t="shared" ref="Q53" si="46">P53*N53</f>
-        <v>0</v>
+        <f t="shared" ref="Q53" si="45">P53*N53</f>
+        <v>1.167</v>
       </c>
       <c r="R53" s="20"/>
     </row>
@@ -4883,7 +5575,7 @@
         <v>179</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>312</v>
@@ -4891,12 +5583,14 @@
       <c r="H54" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="I54" s="14"/>
+      <c r="I54" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J54" s="14" t="s">
         <v>442</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L54" s="14">
         <v>1</v>
@@ -4905,12 +5599,18 @@
         <f>L54*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="14"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="15"/>
+      <c r="N54" s="14">
+        <v>10</v>
+      </c>
+      <c r="O54" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P54" s="45" t="s">
+        <v>604</v>
+      </c>
       <c r="Q54" s="15">
         <f>P54*N54</f>
-        <v>0</v>
+        <v>1.7430000000000001</v>
       </c>
       <c r="R54" s="14"/>
     </row>
@@ -4930,7 +5630,7 @@
         <v>180</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>250</v>
@@ -4938,26 +5638,34 @@
       <c r="H55" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="I55" s="20"/>
+      <c r="I55" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J55" s="20" t="s">
         <v>443</v>
       </c>
       <c r="K55" s="20" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L55" s="20">
         <v>1</v>
       </c>
       <c r="M55" s="20">
-        <f t="shared" ref="M55" si="47">L55*5</f>
+        <f t="shared" ref="M55" si="46">L55*5</f>
         <v>5</v>
       </c>
-      <c r="N55" s="20"/>
-      <c r="O55" s="20"/>
-      <c r="P55" s="21"/>
+      <c r="N55" s="20">
+        <v>10</v>
+      </c>
+      <c r="O55" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P55" s="45" t="s">
+        <v>605</v>
+      </c>
       <c r="Q55" s="21">
-        <f t="shared" ref="Q55" si="48">P55*N55</f>
-        <v>0</v>
+        <f t="shared" ref="Q55" si="47">P55*N55</f>
+        <v>3.5210000000000004</v>
       </c>
       <c r="R55" s="20"/>
     </row>
@@ -4977,7 +5685,7 @@
         <v>181</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G56" s="14" t="s">
         <v>251</v>
@@ -4985,12 +5693,14 @@
       <c r="H56" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="I56" s="14"/>
+      <c r="I56" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J56" s="14" t="s">
         <v>444</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L56" s="14">
         <v>1</v>
@@ -4999,12 +5709,18 @@
         <f>L56*5</f>
         <v>5</v>
       </c>
-      <c r="N56" s="14"/>
-      <c r="O56" s="14"/>
-      <c r="P56" s="15"/>
+      <c r="N56" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O56" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P56" s="45" t="s">
+        <v>606</v>
+      </c>
       <c r="Q56" s="15">
         <f>P56*N56</f>
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="R56" s="14"/>
     </row>
@@ -5032,26 +5748,34 @@
       <c r="H57" s="20" t="s">
         <v>372</v>
       </c>
-      <c r="I57" s="20"/>
+      <c r="I57" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J57" s="20" t="s">
         <v>445</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L57" s="20">
         <v>1</v>
       </c>
       <c r="M57" s="20">
-        <f t="shared" ref="M57" si="49">L57*5</f>
+        <f t="shared" ref="M57" si="48">L57*5</f>
         <v>5</v>
       </c>
-      <c r="N57" s="20"/>
-      <c r="O57" s="20"/>
-      <c r="P57" s="21"/>
+      <c r="N57" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="O57" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P57" s="45" t="s">
+        <v>607</v>
+      </c>
       <c r="Q57" s="21">
-        <f t="shared" ref="Q57" si="50">P57*N57</f>
-        <v>0</v>
+        <f t="shared" ref="Q57" si="49">P57*N57</f>
+        <v>0.64799999999999991</v>
       </c>
       <c r="R57" s="20"/>
     </row>
@@ -5079,12 +5803,14 @@
       <c r="H58" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="I58" s="14"/>
+      <c r="I58" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J58" s="14" t="s">
         <v>446</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L58" s="14">
         <v>2</v>
@@ -5093,12 +5819,18 @@
         <f>L58*5</f>
         <v>10</v>
       </c>
-      <c r="N58" s="14"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="15"/>
+      <c r="N58" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="O58" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P58" s="45" t="s">
+        <v>608</v>
+      </c>
       <c r="Q58" s="15">
         <f>P58*N58</f>
-        <v>0</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="R58" s="14"/>
     </row>
@@ -5126,26 +5858,34 @@
       <c r="H59" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I59" s="20"/>
+      <c r="I59" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J59" s="20" t="s">
         <v>447</v>
       </c>
       <c r="K59" s="20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="L59" s="20">
         <v>2</v>
       </c>
       <c r="M59" s="20">
-        <f t="shared" ref="M59" si="51">L59*5</f>
+        <f t="shared" ref="M59" si="50">L59*5</f>
         <v>10</v>
       </c>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="21"/>
+      <c r="N59" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O59" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P59" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q59" s="21">
-        <f t="shared" ref="Q59" si="52">P59*N59</f>
-        <v>0</v>
+        <f t="shared" ref="Q59" si="51">P59*N59</f>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R59" s="20"/>
     </row>
@@ -5173,12 +5913,14 @@
       <c r="H60" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I60" s="14"/>
+      <c r="I60" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J60" s="14" t="s">
         <v>448</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L60" s="14">
         <v>11</v>
@@ -5187,12 +5929,18 @@
         <f>L60*5</f>
         <v>55</v>
       </c>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="15"/>
+      <c r="N60" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O60" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P60" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q60" s="15">
         <f>P60*N60</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R60" s="14"/>
     </row>
@@ -5220,26 +5968,34 @@
       <c r="H61" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I61" s="20"/>
+      <c r="I61" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J61" s="20" t="s">
         <v>449</v>
       </c>
       <c r="K61" s="20" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L61" s="20">
         <v>23</v>
       </c>
       <c r="M61" s="20">
-        <f t="shared" ref="M61" si="53">L61*5</f>
+        <f t="shared" ref="M61" si="52">L61*5</f>
         <v>115</v>
       </c>
-      <c r="N61" s="20"/>
-      <c r="O61" s="20"/>
-      <c r="P61" s="21"/>
+      <c r="N61" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="O61" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P61" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q61" s="21">
-        <f t="shared" ref="Q61" si="54">P61*N61</f>
-        <v>0</v>
+        <f t="shared" ref="Q61" si="53">P61*N61</f>
+        <v>0.12</v>
       </c>
       <c r="R61" s="20"/>
     </row>
@@ -5267,12 +6023,14 @@
       <c r="H62" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I62" s="14"/>
+      <c r="I62" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J62" s="14" t="s">
         <v>450</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="L62" s="14">
         <v>2</v>
@@ -5281,12 +6039,18 @@
         <f>L62*5</f>
         <v>10</v>
       </c>
-      <c r="N62" s="14"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="15"/>
+      <c r="N62" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O62" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P62" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q62" s="15">
         <f>P62*N62</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R62" s="14"/>
     </row>
@@ -5314,26 +6078,34 @@
       <c r="H63" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I63" s="20"/>
+      <c r="I63" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J63" s="20" t="s">
         <v>451</v>
       </c>
       <c r="K63" s="20" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L63" s="20">
         <v>4</v>
       </c>
       <c r="M63" s="20">
-        <f t="shared" ref="M63" si="55">L63*5</f>
+        <f t="shared" ref="M63" si="54">L63*5</f>
         <v>20</v>
       </c>
-      <c r="N63" s="20"/>
-      <c r="O63" s="20"/>
-      <c r="P63" s="21"/>
+      <c r="N63" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O63" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P63" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q63" s="21">
-        <f t="shared" ref="Q63" si="56">P63*N63</f>
-        <v>0</v>
+        <f t="shared" ref="Q63" si="55">P63*N63</f>
+        <v>0.06</v>
       </c>
       <c r="R63" s="20"/>
     </row>
@@ -5361,12 +6133,14 @@
       <c r="H64" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I64" s="14"/>
+      <c r="I64" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J64" s="14" t="s">
         <v>452</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="L64" s="14">
         <v>2</v>
@@ -5375,12 +6149,18 @@
         <f>L64*5</f>
         <v>10</v>
       </c>
-      <c r="N64" s="14"/>
-      <c r="O64" s="14"/>
-      <c r="P64" s="15"/>
+      <c r="N64" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O64" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P64" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q64" s="15">
         <f>P64*N64</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R64" s="14"/>
     </row>
@@ -5408,26 +6188,34 @@
       <c r="H65" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="I65" s="20"/>
+      <c r="I65" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J65" s="20" t="s">
         <v>453</v>
       </c>
       <c r="K65" s="20" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="L65" s="20">
         <v>1</v>
       </c>
       <c r="M65" s="20">
-        <f t="shared" ref="M65" si="57">L65*5</f>
+        <f t="shared" ref="M65" si="56">L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
-      <c r="P65" s="21"/>
+      <c r="N65" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O65" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P65" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q65" s="21">
-        <f t="shared" ref="Q65" si="58">P65*N65</f>
-        <v>0</v>
+        <f t="shared" ref="Q65" si="57">P65*N65</f>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R65" s="20"/>
     </row>
@@ -5455,12 +6243,14 @@
       <c r="H66" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I66" s="14"/>
+      <c r="I66" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J66" s="14" t="s">
         <v>454</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="L66" s="14">
         <v>16</v>
@@ -5469,12 +6259,18 @@
         <f>L66*5</f>
         <v>80</v>
       </c>
-      <c r="N66" s="14"/>
-      <c r="O66" s="14"/>
-      <c r="P66" s="15"/>
+      <c r="N66" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O66" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P66" s="45" t="s">
+        <v>610</v>
+      </c>
       <c r="Q66" s="15">
         <f>P66*N66</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R66" s="14"/>
     </row>
@@ -5502,26 +6298,34 @@
       <c r="H67" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I67" s="20"/>
+      <c r="I67" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J67" s="20" t="s">
         <v>455</v>
       </c>
       <c r="K67" s="20" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L67" s="20">
         <v>1</v>
       </c>
       <c r="M67" s="20">
-        <f t="shared" ref="M67" si="59">L67*5</f>
+        <f t="shared" ref="M67" si="58">L67*5</f>
         <v>5</v>
       </c>
-      <c r="N67" s="20"/>
-      <c r="O67" s="20"/>
-      <c r="P67" s="21"/>
+      <c r="N67" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O67" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P67" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q67" s="21">
-        <f t="shared" ref="Q67" si="60">P67*N67</f>
-        <v>0</v>
+        <f t="shared" ref="Q67" si="59">P67*N67</f>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R67" s="20"/>
     </row>
@@ -5549,12 +6353,14 @@
       <c r="H68" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I68" s="14"/>
+      <c r="I68" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J68" s="14" t="s">
         <v>456</v>
       </c>
       <c r="K68" s="14" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="L68" s="14">
         <v>1</v>
@@ -5563,12 +6369,18 @@
         <f>L68*5</f>
         <v>5</v>
       </c>
-      <c r="N68" s="14"/>
-      <c r="O68" s="14"/>
-      <c r="P68" s="15"/>
+      <c r="N68" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O68" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P68" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q68" s="15">
         <f>P68*N68</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="R68" s="14"/>
     </row>
@@ -5596,26 +6408,34 @@
       <c r="H69" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I69" s="20"/>
+      <c r="I69" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J69" s="20" t="s">
         <v>457</v>
       </c>
       <c r="K69" s="20" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L69" s="20">
         <v>10</v>
       </c>
       <c r="M69" s="20">
-        <f t="shared" ref="M69" si="61">L69*5</f>
+        <f t="shared" ref="M69" si="60">L69*5</f>
         <v>50</v>
       </c>
-      <c r="N69" s="20"/>
-      <c r="O69" s="20"/>
-      <c r="P69" s="21"/>
+      <c r="N69" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O69" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P69" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q69" s="21">
-        <f t="shared" ref="Q69" si="62">P69*N69</f>
-        <v>0</v>
+        <f t="shared" ref="Q69" si="61">P69*N69</f>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R69" s="20"/>
     </row>
@@ -5643,12 +6463,14 @@
       <c r="H70" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I70" s="14"/>
+      <c r="I70" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J70" s="14" t="s">
         <v>458</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L70" s="14">
         <v>1</v>
@@ -5657,12 +6479,18 @@
         <f>L70*5</f>
         <v>5</v>
       </c>
-      <c r="N70" s="14"/>
-      <c r="O70" s="14"/>
-      <c r="P70" s="15"/>
+      <c r="N70" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O70" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P70" s="45" t="s">
+        <v>611</v>
+      </c>
       <c r="Q70" s="15">
         <f>P70*N70</f>
-        <v>0</v>
+        <v>0.45600000000000002</v>
       </c>
       <c r="R70" s="14"/>
     </row>
@@ -5690,26 +6518,34 @@
       <c r="H71" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I71" s="20"/>
+      <c r="I71" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J71" s="20" t="s">
         <v>459</v>
       </c>
       <c r="K71" s="20" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="L71" s="20">
         <v>1</v>
       </c>
       <c r="M71" s="20">
-        <f t="shared" ref="M71" si="63">L71*5</f>
+        <f t="shared" ref="M71" si="62">L71*5</f>
         <v>5</v>
       </c>
-      <c r="N71" s="20"/>
-      <c r="O71" s="20"/>
-      <c r="P71" s="21"/>
+      <c r="N71" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O71" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P71" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q71" s="21">
-        <f t="shared" ref="Q71" si="64">P71*N71</f>
-        <v>0</v>
+        <f t="shared" ref="Q71" si="63">P71*N71</f>
+        <v>0.06</v>
       </c>
       <c r="R71" s="20"/>
     </row>
@@ -5737,12 +6573,14 @@
       <c r="H72" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I72" s="14"/>
+      <c r="I72" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J72" s="14" t="s">
         <v>460</v>
       </c>
       <c r="K72" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="L72" s="14">
         <v>1</v>
@@ -5751,12 +6589,18 @@
         <f>L72*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="14"/>
-      <c r="O72" s="14"/>
-      <c r="P72" s="15"/>
+      <c r="N72" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O72" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P72" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q72" s="15">
         <f>P72*N72</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R72" s="14"/>
     </row>
@@ -5784,26 +6628,34 @@
       <c r="H73" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I73" s="20"/>
+      <c r="I73" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J73" s="20" t="s">
         <v>461</v>
       </c>
       <c r="K73" s="20" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="L73" s="20">
         <v>1</v>
       </c>
       <c r="M73" s="20">
-        <f t="shared" ref="M73" si="65">L73*5</f>
+        <f t="shared" ref="M73" si="64">L73*5</f>
         <v>5</v>
       </c>
-      <c r="N73" s="20"/>
-      <c r="O73" s="20"/>
-      <c r="P73" s="21"/>
+      <c r="N73" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O73" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P73" s="45" t="s">
+        <v>612</v>
+      </c>
       <c r="Q73" s="21">
-        <f t="shared" ref="Q73" si="66">P73*N73</f>
-        <v>0</v>
+        <f t="shared" ref="Q73" si="65">P73*N73</f>
+        <v>0.96</v>
       </c>
       <c r="R73" s="20"/>
     </row>
@@ -5831,12 +6683,14 @@
       <c r="H74" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I74" s="14"/>
+      <c r="I74" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J74" s="14" t="s">
         <v>462</v>
       </c>
       <c r="K74" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="L74" s="14">
         <v>1</v>
@@ -5845,12 +6699,18 @@
         <f>L74*5</f>
         <v>5</v>
       </c>
-      <c r="N74" s="14"/>
-      <c r="O74" s="14"/>
-      <c r="P74" s="15"/>
+      <c r="N74" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O74" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P74" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q74" s="15">
         <f>P74*N74</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R74" s="14"/>
     </row>
@@ -5878,26 +6738,34 @@
       <c r="H75" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I75" s="20"/>
+      <c r="I75" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J75" s="20" t="s">
         <v>463</v>
       </c>
       <c r="K75" s="20" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="L75" s="20">
         <v>1</v>
       </c>
       <c r="M75" s="20">
-        <f t="shared" ref="M75" si="67">L75*5</f>
+        <f t="shared" ref="M75" si="66">L75*5</f>
         <v>5</v>
       </c>
-      <c r="N75" s="20"/>
-      <c r="O75" s="20"/>
-      <c r="P75" s="21"/>
+      <c r="N75" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="O75" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P75" s="45" t="s">
+        <v>613</v>
+      </c>
       <c r="Q75" s="21">
-        <f t="shared" ref="Q75" si="68">P75*N75</f>
-        <v>0</v>
+        <f t="shared" ref="Q75" si="67">P75*N75</f>
+        <v>0.41799999999999998</v>
       </c>
       <c r="R75" s="20"/>
     </row>
@@ -5910,43 +6778,53 @@
       <c r="C76" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="F76" s="14" t="s">
+      <c r="F76" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="53" t="s">
         <v>317</v>
       </c>
-      <c r="H76" s="14" t="s">
+      <c r="H76" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14" t="s">
+      <c r="I76" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J76" s="53" t="s">
         <v>449</v>
       </c>
-      <c r="K76" s="14" t="s">
-        <v>512</v>
-      </c>
-      <c r="L76" s="14">
+      <c r="K76" s="53" t="s">
+        <v>510</v>
+      </c>
+      <c r="L76" s="53">
         <v>16</v>
       </c>
-      <c r="M76" s="14">
+      <c r="M76" s="53">
         <f>L76*5</f>
         <v>80</v>
       </c>
-      <c r="N76" s="14"/>
-      <c r="O76" s="14"/>
-      <c r="P76" s="15"/>
-      <c r="Q76" s="15">
+      <c r="N76" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="O76" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P76" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q76" s="54">
         <f>P76*N76</f>
-        <v>0</v>
-      </c>
-      <c r="R76" s="14"/>
+        <v>0.06</v>
+      </c>
+      <c r="R76" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="1"/>
@@ -5972,26 +6850,34 @@
       <c r="H77" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I77" s="20"/>
+      <c r="I77" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J77" s="20" t="s">
         <v>464</v>
       </c>
       <c r="K77" s="20" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="L77" s="20">
         <v>1</v>
       </c>
       <c r="M77" s="20">
-        <f t="shared" ref="M77" si="69">L77*5</f>
+        <f t="shared" ref="M77" si="68">L77*5</f>
         <v>5</v>
       </c>
-      <c r="N77" s="20"/>
-      <c r="O77" s="20"/>
-      <c r="P77" s="21"/>
+      <c r="N77" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O77" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P77" s="45" t="s">
+        <v>614</v>
+      </c>
       <c r="Q77" s="21">
-        <f t="shared" ref="Q77" si="70">P77*N77</f>
-        <v>0</v>
+        <f t="shared" ref="Q77" si="69">P77*N77</f>
+        <v>0.5</v>
       </c>
       <c r="R77" s="20"/>
     </row>
@@ -6019,12 +6905,14 @@
       <c r="H78" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I78" s="14"/>
+      <c r="I78" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J78" s="14" t="s">
         <v>465</v>
       </c>
       <c r="K78" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="L78" s="14">
         <v>1</v>
@@ -6033,12 +6921,18 @@
         <f>L78*5</f>
         <v>5</v>
       </c>
-      <c r="N78" s="14"/>
-      <c r="O78" s="14"/>
-      <c r="P78" s="15"/>
+      <c r="N78" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O78" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P78" s="45" t="s">
+        <v>615</v>
+      </c>
       <c r="Q78" s="15">
         <f>P78*N78</f>
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="R78" s="14"/>
     </row>
@@ -6066,26 +6960,34 @@
       <c r="H79" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I79" s="20"/>
+      <c r="I79" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J79" s="20" t="s">
         <v>466</v>
       </c>
       <c r="K79" s="20" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L79" s="20">
         <v>1</v>
       </c>
       <c r="M79" s="20">
-        <f t="shared" ref="M79" si="71">L79*5</f>
+        <f t="shared" ref="M79" si="70">L79*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="20"/>
-      <c r="O79" s="20"/>
-      <c r="P79" s="21"/>
+      <c r="N79" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O79" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P79" s="45" t="s">
+        <v>616</v>
+      </c>
       <c r="Q79" s="21">
-        <f t="shared" ref="Q79" si="72">P79*N79</f>
-        <v>0</v>
+        <f t="shared" ref="Q79" si="71">P79*N79</f>
+        <v>0.09</v>
       </c>
       <c r="R79" s="20"/>
     </row>
@@ -6098,43 +7000,52 @@
       <c r="C80" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="53" t="s">
         <v>322</v>
       </c>
-      <c r="H80" s="14" t="s">
+      <c r="H80" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14" t="s">
+      <c r="I80" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J80" s="53" t="s">
         <v>454</v>
       </c>
-      <c r="K80" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="L80" s="14">
+      <c r="K80" s="53" t="s">
+        <v>507</v>
+      </c>
+      <c r="L80" s="53">
         <v>1</v>
       </c>
-      <c r="M80" s="14">
+      <c r="M80" s="53">
         <f>L80*5</f>
         <v>5</v>
       </c>
-      <c r="N80" s="14"/>
-      <c r="O80" s="14"/>
-      <c r="P80" s="15"/>
-      <c r="Q80" s="15">
-        <f>P80*N80</f>
-        <v>0</v>
-      </c>
-      <c r="R80" s="14"/>
+      <c r="N80" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="O80" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P80" s="51" t="s">
+        <v>559</v>
+      </c>
+      <c r="Q80" s="54" t="s">
+        <v>559</v>
+      </c>
+      <c r="R80" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="1"/>
@@ -6160,26 +7071,34 @@
       <c r="H81" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I81" s="20"/>
+      <c r="I81" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J81" s="20" t="s">
         <v>467</v>
       </c>
       <c r="K81" s="20" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L81" s="20">
         <v>5</v>
       </c>
       <c r="M81" s="20">
-        <f t="shared" ref="M81" si="73">L81*5</f>
+        <f t="shared" ref="M81" si="72">L81*5</f>
         <v>25</v>
       </c>
-      <c r="N81" s="20"/>
-      <c r="O81" s="20"/>
-      <c r="P81" s="21"/>
+      <c r="N81" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O81" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P81" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q81" s="21">
-        <f t="shared" ref="Q81" si="74">P81*N81</f>
-        <v>0</v>
+        <f t="shared" ref="Q81" si="73">P81*N81</f>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R81" s="20"/>
     </row>
@@ -6207,12 +7126,14 @@
       <c r="H82" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I82" s="14"/>
+      <c r="I82" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J82" s="14" t="s">
         <v>468</v>
       </c>
       <c r="K82" s="14" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="L82" s="14">
         <v>8</v>
@@ -6221,12 +7142,18 @@
         <f>L82*5</f>
         <v>40</v>
       </c>
-      <c r="N82" s="14"/>
-      <c r="O82" s="14"/>
-      <c r="P82" s="15"/>
+      <c r="N82" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O82" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P82" s="45" t="s">
+        <v>588</v>
+      </c>
       <c r="Q82" s="15">
         <f>P82*N82</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R82" s="14"/>
     </row>
@@ -6254,26 +7181,34 @@
       <c r="H83" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I83" s="20"/>
+      <c r="I83" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J83" s="20" t="s">
         <v>469</v>
       </c>
       <c r="K83" s="20" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="L83" s="20">
         <v>4</v>
       </c>
       <c r="M83" s="20">
-        <f t="shared" ref="M83" si="75">L83*5</f>
+        <f t="shared" ref="M83" si="74">L83*5</f>
         <v>20</v>
       </c>
-      <c r="N83" s="20"/>
-      <c r="O83" s="20"/>
-      <c r="P83" s="21"/>
+      <c r="N83" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O83" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P83" s="45" t="s">
+        <v>616</v>
+      </c>
       <c r="Q83" s="21">
-        <f t="shared" ref="Q83" si="76">P83*N83</f>
-        <v>0</v>
+        <f t="shared" ref="Q83" si="75">P83*N83</f>
+        <v>0.09</v>
       </c>
       <c r="R83" s="20"/>
     </row>
@@ -6301,12 +7236,14 @@
       <c r="H84" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I84" s="14"/>
+      <c r="I84" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J84" s="14" t="s">
         <v>470</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="L84" s="14">
         <v>1</v>
@@ -6315,12 +7252,18 @@
         <f>L84*5</f>
         <v>5</v>
       </c>
-      <c r="N84" s="14"/>
-      <c r="O84" s="14"/>
-      <c r="P84" s="15"/>
+      <c r="N84" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O84" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P84" s="45" t="s">
+        <v>617</v>
+      </c>
       <c r="Q84" s="15">
         <f>P84*N84</f>
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="R84" s="14"/>
     </row>
@@ -6333,43 +7276,53 @@
       <c r="C85" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="20" t="s">
+      <c r="D85" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="E85" s="20" t="s">
+      <c r="E85" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="F85" s="20" t="s">
+      <c r="F85" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="G85" s="20" t="s">
+      <c r="G85" s="53" t="s">
         <v>339</v>
       </c>
-      <c r="H85" s="20" t="s">
+      <c r="H85" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="I85" s="20"/>
-      <c r="J85" s="20" t="s">
+      <c r="I85" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J85" s="53" t="s">
         <v>471</v>
       </c>
-      <c r="K85" s="20" t="s">
-        <v>539</v>
-      </c>
-      <c r="L85" s="20">
+      <c r="K85" s="53" t="s">
+        <v>537</v>
+      </c>
+      <c r="L85" s="53">
         <v>4</v>
       </c>
-      <c r="M85" s="20">
-        <f t="shared" ref="M85" si="77">L85*5</f>
+      <c r="M85" s="53">
+        <f t="shared" ref="M85" si="76">L85*5</f>
         <v>20</v>
       </c>
-      <c r="N85" s="20"/>
-      <c r="O85" s="20"/>
-      <c r="P85" s="21"/>
-      <c r="Q85" s="21">
-        <f t="shared" ref="Q85" si="78">P85*N85</f>
-        <v>0</v>
-      </c>
-      <c r="R85" s="20"/>
+      <c r="N85" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="O85" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P85" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q85" s="54">
+        <f t="shared" ref="Q85" si="77">P85*N85</f>
+        <v>0.06</v>
+      </c>
+      <c r="R85" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="1"/>
@@ -6395,12 +7348,14 @@
       <c r="H86" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I86" s="14"/>
+      <c r="I86" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J86" s="14" t="s">
         <v>471</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L86" s="14">
         <v>5</v>
@@ -6409,12 +7364,18 @@
         <f>L86*5</f>
         <v>25</v>
       </c>
-      <c r="N86" s="14"/>
-      <c r="O86" s="14"/>
-      <c r="P86" s="15"/>
+      <c r="N86" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O86" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P86" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q86" s="15">
         <f>P86*N86</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="R86" s="14"/>
     </row>
@@ -6442,26 +7403,34 @@
       <c r="H87" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I87" s="20"/>
+      <c r="I87" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J87" s="20" t="s">
-        <v>472</v>
+        <v>649</v>
       </c>
       <c r="K87" s="20" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L87" s="20">
         <v>1</v>
       </c>
       <c r="M87" s="20">
-        <f t="shared" ref="M87" si="79">L87*5</f>
+        <f t="shared" ref="M87" si="78">L87*5</f>
         <v>5</v>
       </c>
-      <c r="N87" s="20"/>
-      <c r="O87" s="20"/>
-      <c r="P87" s="21"/>
+      <c r="N87" s="20">
+        <v>100</v>
+      </c>
+      <c r="O87" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P87" s="45">
+        <v>2E-3</v>
+      </c>
       <c r="Q87" s="21">
-        <f t="shared" ref="Q87" si="80">P87*N87</f>
-        <v>0</v>
+        <f t="shared" ref="Q87" si="79">P87*N87</f>
+        <v>0.2</v>
       </c>
       <c r="R87" s="20"/>
     </row>
@@ -6474,43 +7443,53 @@
       <c r="C88" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="D88" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="F88" s="14" t="s">
+      <c r="F88" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="G88" s="53" t="s">
         <v>317</v>
       </c>
-      <c r="H88" s="14" t="s">
+      <c r="H88" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="14"/>
-      <c r="J88" s="14" t="s">
+      <c r="I88" s="57" t="s">
+        <v>650</v>
+      </c>
+      <c r="J88" s="53" t="s">
         <v>449</v>
       </c>
-      <c r="K88" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="L88" s="14">
+      <c r="K88" s="53" t="s">
+        <v>537</v>
+      </c>
+      <c r="L88" s="53">
         <v>1</v>
       </c>
-      <c r="M88" s="14">
+      <c r="M88" s="53">
         <f>L88*5</f>
         <v>5</v>
       </c>
-      <c r="N88" s="14"/>
-      <c r="O88" s="14"/>
-      <c r="P88" s="15"/>
-      <c r="Q88" s="15">
+      <c r="N88" s="53" t="s">
+        <v>640</v>
+      </c>
+      <c r="O88" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="P88" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q88" s="54">
         <f>P88*N88</f>
-        <v>0</v>
-      </c>
-      <c r="R88" s="14"/>
+        <v>0.06</v>
+      </c>
+      <c r="R88" s="55" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="89" spans="1:18">
       <c r="A89" s="1"/>
@@ -6536,26 +7515,34 @@
       <c r="H89" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I89" s="20"/>
+      <c r="I89" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J89" s="20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K89" s="20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="L89" s="20">
         <v>1</v>
       </c>
       <c r="M89" s="20">
-        <f t="shared" ref="M89" si="81">L89*5</f>
+        <f t="shared" ref="M89" si="80">L89*5</f>
         <v>5</v>
       </c>
-      <c r="N89" s="20"/>
-      <c r="O89" s="20"/>
-      <c r="P89" s="21"/>
+      <c r="N89" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="O89" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P89" s="45" t="s">
+        <v>588</v>
+      </c>
       <c r="Q89" s="21">
-        <f t="shared" ref="Q89" si="82">P89*N89</f>
-        <v>0</v>
+        <f t="shared" ref="Q89" si="81">P89*N89</f>
+        <v>0.13</v>
       </c>
       <c r="R89" s="20"/>
     </row>
@@ -6583,12 +7570,14 @@
       <c r="H90" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I90" s="14"/>
+      <c r="I90" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J90" s="14" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="L90" s="14">
         <v>1</v>
@@ -6597,12 +7586,18 @@
         <f>L90*5</f>
         <v>5</v>
       </c>
-      <c r="N90" s="14"/>
-      <c r="O90" s="14"/>
-      <c r="P90" s="15"/>
+      <c r="N90" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="O90" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P90" s="45" t="s">
+        <v>618</v>
+      </c>
       <c r="Q90" s="15">
         <f>P90*N90</f>
-        <v>0</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="R90" s="14"/>
     </row>
@@ -6630,26 +7625,34 @@
       <c r="H91" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I91" s="20"/>
+      <c r="I91" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J91" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K91" s="20" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L91" s="20">
         <v>1</v>
       </c>
       <c r="M91" s="20">
-        <f t="shared" ref="M91" si="83">L91*5</f>
+        <f t="shared" ref="M91" si="82">L91*5</f>
         <v>5</v>
       </c>
-      <c r="N91" s="20"/>
-      <c r="O91" s="20"/>
-      <c r="P91" s="21"/>
+      <c r="N91" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O91" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P91" s="45" t="s">
+        <v>619</v>
+      </c>
       <c r="Q91" s="21">
-        <f t="shared" ref="Q91" si="84">P91*N91</f>
-        <v>0</v>
+        <f t="shared" ref="Q91" si="83">P91*N91</f>
+        <v>0.97</v>
       </c>
       <c r="R91" s="20"/>
     </row>
@@ -6677,10 +7680,14 @@
       <c r="H92" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I92" s="14"/>
-      <c r="J92" s="14"/>
+      <c r="I92" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="J92" s="14" t="s">
+        <v>652</v>
+      </c>
       <c r="K92" s="14" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L92" s="14">
         <v>2</v>
@@ -6689,12 +7696,18 @@
         <f>L92*5</f>
         <v>10</v>
       </c>
-      <c r="N92" s="14"/>
-      <c r="O92" s="14"/>
-      <c r="P92" s="15"/>
+      <c r="N92" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O92" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P92" s="45" t="s">
+        <v>609</v>
+      </c>
       <c r="Q92" s="15">
         <f>P92*N92</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R92" s="14"/>
     </row>
@@ -6722,26 +7735,34 @@
       <c r="H93" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I93" s="20"/>
+      <c r="I93" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J93" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K93" s="20" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="L93" s="20">
         <v>2</v>
       </c>
       <c r="M93" s="20">
-        <f t="shared" ref="M93" si="85">L93*5</f>
+        <f t="shared" ref="M93" si="84">L93*5</f>
         <v>10</v>
       </c>
-      <c r="N93" s="20"/>
-      <c r="O93" s="20"/>
-      <c r="P93" s="21"/>
+      <c r="N93" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="O93" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P93" s="45" t="s">
+        <v>620</v>
+      </c>
       <c r="Q93" s="21">
-        <f t="shared" ref="Q93" si="86">P93*N93</f>
-        <v>0</v>
+        <f t="shared" ref="Q93" si="85">P93*N93</f>
+        <v>1.01</v>
       </c>
       <c r="R93" s="20"/>
     </row>
@@ -6769,10 +7790,14 @@
       <c r="H94" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I94" s="14"/>
-      <c r="J94" s="14"/>
+      <c r="I94" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>653</v>
+      </c>
       <c r="K94" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L94" s="14">
         <v>5</v>
@@ -6781,12 +7806,18 @@
         <f>L94*5</f>
         <v>25</v>
       </c>
-      <c r="N94" s="14"/>
-      <c r="O94" s="14"/>
-      <c r="P94" s="15"/>
+      <c r="N94" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="O94" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P94" s="45" t="s">
+        <v>581</v>
+      </c>
       <c r="Q94" s="15">
         <f>P94*N94</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="R94" s="14"/>
     </row>
@@ -6806,7 +7837,7 @@
         <v>216</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G95" s="20" t="s">
         <v>257</v>
@@ -6814,26 +7845,34 @@
       <c r="H95" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="I95" s="20"/>
+      <c r="I95" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J95" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K95" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L95" s="20">
         <v>3</v>
       </c>
       <c r="M95" s="20">
-        <f t="shared" ref="M95" si="87">L95*5</f>
+        <f t="shared" ref="M95" si="86">L95*5</f>
         <v>15</v>
       </c>
-      <c r="N95" s="20"/>
-      <c r="O95" s="20"/>
-      <c r="P95" s="21"/>
+      <c r="N95" s="20">
+        <v>20</v>
+      </c>
+      <c r="O95" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P95" s="45" t="s">
+        <v>621</v>
+      </c>
       <c r="Q95" s="21">
-        <f t="shared" ref="Q95" si="88">P95*N95</f>
-        <v>0</v>
+        <f t="shared" ref="Q95" si="87">P95*N95</f>
+        <v>3.0339999999999998</v>
       </c>
       <c r="R95" s="20"/>
     </row>
@@ -6861,12 +7900,14 @@
       <c r="H96" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="I96" s="14"/>
+      <c r="I96" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J96" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K96" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L96" s="14">
         <v>1</v>
@@ -6875,12 +7916,18 @@
         <f>L96*5</f>
         <v>5</v>
       </c>
-      <c r="N96" s="14"/>
-      <c r="O96" s="14"/>
-      <c r="P96" s="15"/>
+      <c r="N96" s="14">
+        <v>6</v>
+      </c>
+      <c r="O96" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P96" s="45" t="s">
+        <v>622</v>
+      </c>
       <c r="Q96" s="15">
         <f>P96*N96</f>
-        <v>0</v>
+        <v>65.206199999999995</v>
       </c>
       <c r="R96" s="14"/>
     </row>
@@ -6908,24 +7955,32 @@
       <c r="H97" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="I97" s="20"/>
+      <c r="I97" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J97" s="20"/>
       <c r="K97" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L97" s="20">
         <v>1</v>
       </c>
       <c r="M97" s="20">
-        <f t="shared" ref="M97" si="89">L97*5</f>
+        <f t="shared" ref="M97" si="88">L97*5</f>
         <v>5</v>
       </c>
-      <c r="N97" s="20"/>
-      <c r="O97" s="20"/>
-      <c r="P97" s="21"/>
+      <c r="N97" s="20">
+        <v>6</v>
+      </c>
+      <c r="O97" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P97" s="45" t="s">
+        <v>623</v>
+      </c>
       <c r="Q97" s="21">
-        <f t="shared" ref="Q97" si="90">P97*N97</f>
-        <v>0</v>
+        <f t="shared" ref="Q97" si="89">P97*N97</f>
+        <v>5.4792000000000005</v>
       </c>
       <c r="R97" s="20"/>
     </row>
@@ -6953,12 +8008,14 @@
       <c r="H98" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="I98" s="14"/>
+      <c r="I98" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J98" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K98" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L98" s="14">
         <v>1</v>
@@ -6967,12 +8024,18 @@
         <f>L98*5</f>
         <v>5</v>
       </c>
-      <c r="N98" s="14"/>
-      <c r="O98" s="14"/>
-      <c r="P98" s="15"/>
+      <c r="N98" s="14">
+        <v>6</v>
+      </c>
+      <c r="O98" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P98" s="45" t="s">
+        <v>624</v>
+      </c>
       <c r="Q98" s="15">
         <f>P98*N98</f>
-        <v>0</v>
+        <v>21.375600000000002</v>
       </c>
       <c r="R98" s="14"/>
     </row>
@@ -7000,26 +8063,34 @@
       <c r="H99" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="I99" s="20"/>
-      <c r="J99" s="20" t="s">
-        <v>480</v>
+      <c r="I99" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="J99" s="14" t="s">
+        <v>559</v>
       </c>
       <c r="K99" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L99" s="20">
         <v>1</v>
       </c>
       <c r="M99" s="20">
-        <f t="shared" ref="M99" si="91">L99*5</f>
+        <f t="shared" ref="M99" si="90">L99*5</f>
         <v>5</v>
       </c>
-      <c r="N99" s="20"/>
-      <c r="O99" s="20"/>
-      <c r="P99" s="21"/>
+      <c r="N99" s="14">
+        <v>6</v>
+      </c>
+      <c r="O99" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="P99" s="45">
+        <v>9.16</v>
+      </c>
       <c r="Q99" s="21">
-        <f t="shared" ref="Q99" si="92">P99*N99</f>
-        <v>0</v>
+        <f t="shared" ref="Q99" si="91">P99*N99</f>
+        <v>54.96</v>
       </c>
       <c r="R99" s="20"/>
     </row>
@@ -7047,12 +8118,14 @@
       <c r="H100" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="I100" s="14"/>
+      <c r="I100" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J100" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="K100" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L100" s="14">
         <v>1</v>
@@ -7061,12 +8134,18 @@
         <f>L100*5</f>
         <v>5</v>
       </c>
-      <c r="N100" s="14"/>
-      <c r="O100" s="14"/>
-      <c r="P100" s="15"/>
+      <c r="N100" s="14">
+        <v>6</v>
+      </c>
+      <c r="O100" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P100" s="45" t="s">
+        <v>625</v>
+      </c>
       <c r="Q100" s="15">
         <f>P100*N100</f>
-        <v>0</v>
+        <v>2.8271999999999999</v>
       </c>
       <c r="R100" s="14"/>
     </row>
@@ -7094,26 +8173,34 @@
       <c r="H101" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="I101" s="20"/>
+      <c r="I101" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J101" s="20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K101" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L101" s="20">
         <v>1</v>
       </c>
       <c r="M101" s="20">
-        <f t="shared" ref="M101" si="93">L101*5</f>
+        <f t="shared" ref="M101" si="92">L101*5</f>
         <v>5</v>
       </c>
-      <c r="N101" s="20"/>
-      <c r="O101" s="20"/>
-      <c r="P101" s="21"/>
+      <c r="N101" s="20">
+        <v>6</v>
+      </c>
+      <c r="O101" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P101" s="45" t="s">
+        <v>626</v>
+      </c>
       <c r="Q101" s="21">
-        <f t="shared" ref="Q101" si="94">P101*N101</f>
-        <v>0</v>
+        <f t="shared" ref="Q101" si="93">P101*N101</f>
+        <v>10.353</v>
       </c>
       <c r="R101" s="20"/>
     </row>
@@ -7141,12 +8228,14 @@
       <c r="H102" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="I102" s="14"/>
+      <c r="I102" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J102" s="14" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K102" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L102" s="14">
         <v>1</v>
@@ -7155,12 +8244,18 @@
         <f>L102*5</f>
         <v>5</v>
       </c>
-      <c r="N102" s="14"/>
-      <c r="O102" s="14"/>
-      <c r="P102" s="15"/>
+      <c r="N102" s="14">
+        <v>6</v>
+      </c>
+      <c r="O102" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P102" s="45" t="s">
+        <v>627</v>
+      </c>
       <c r="Q102" s="15">
         <f>P102*N102</f>
-        <v>0</v>
+        <v>17.866199999999999</v>
       </c>
       <c r="R102" s="14"/>
     </row>
@@ -7188,26 +8283,34 @@
       <c r="H103" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="I103" s="20"/>
+      <c r="I103" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J103" s="20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K103" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L103" s="20">
         <v>1</v>
       </c>
       <c r="M103" s="20">
-        <f t="shared" ref="M103" si="95">L103*5</f>
+        <f t="shared" ref="M103" si="94">L103*5</f>
         <v>5</v>
       </c>
-      <c r="N103" s="20"/>
-      <c r="O103" s="20"/>
-      <c r="P103" s="21"/>
+      <c r="N103" s="20">
+        <v>10</v>
+      </c>
+      <c r="O103" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P103" s="45" t="s">
+        <v>628</v>
+      </c>
       <c r="Q103" s="21">
-        <f t="shared" ref="Q103" si="96">P103*N103</f>
-        <v>0</v>
+        <f t="shared" ref="Q103" si="95">P103*N103</f>
+        <v>0.70499999999999996</v>
       </c>
       <c r="R103" s="20"/>
     </row>
@@ -7235,12 +8338,14 @@
       <c r="H104" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="I104" s="14"/>
+      <c r="I104" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J104" s="14" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="K104" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L104" s="14">
         <v>1</v>
@@ -7249,12 +8354,18 @@
         <f>L104*5</f>
         <v>5</v>
       </c>
-      <c r="N104" s="14"/>
-      <c r="O104" s="14"/>
-      <c r="P104" s="15"/>
+      <c r="N104" s="14">
+        <v>10</v>
+      </c>
+      <c r="O104" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P104" s="45" t="s">
+        <v>629</v>
+      </c>
       <c r="Q104" s="15">
         <f>P104*N104</f>
-        <v>0</v>
+        <v>1.554</v>
       </c>
       <c r="R104" s="14"/>
     </row>
@@ -7282,26 +8393,34 @@
       <c r="H105" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="I105" s="20"/>
+      <c r="I105" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J105" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K105" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L105" s="20">
         <v>1</v>
       </c>
       <c r="M105" s="20">
-        <f t="shared" ref="M105" si="97">L105*5</f>
+        <f t="shared" ref="M105" si="96">L105*5</f>
         <v>5</v>
       </c>
-      <c r="N105" s="20"/>
-      <c r="O105" s="20"/>
-      <c r="P105" s="21"/>
+      <c r="N105" s="20">
+        <v>6</v>
+      </c>
+      <c r="O105" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P105" s="45" t="s">
+        <v>630</v>
+      </c>
       <c r="Q105" s="21">
-        <f t="shared" ref="Q105" si="98">P105*N105</f>
-        <v>0</v>
+        <f t="shared" ref="Q105" si="97">P105*N105</f>
+        <v>116.44800000000001</v>
       </c>
       <c r="R105" s="20"/>
     </row>
@@ -7329,12 +8448,14 @@
       <c r="H106" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="I106" s="14"/>
+      <c r="I106" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J106" s="14" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K106" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L106" s="14">
         <v>1</v>
@@ -7343,12 +8464,18 @@
         <f>L106*5</f>
         <v>5</v>
       </c>
-      <c r="N106" s="14"/>
-      <c r="O106" s="14"/>
-      <c r="P106" s="15"/>
+      <c r="N106" s="14">
+        <v>6</v>
+      </c>
+      <c r="O106" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P106" s="45" t="s">
+        <v>631</v>
+      </c>
       <c r="Q106" s="15">
         <f>P106*N106</f>
-        <v>0</v>
+        <v>3.5693999999999999</v>
       </c>
       <c r="R106" s="14"/>
     </row>
@@ -7376,26 +8503,34 @@
       <c r="H107" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="I107" s="20"/>
+      <c r="I107" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J107" s="20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K107" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L107" s="20">
         <v>1</v>
       </c>
       <c r="M107" s="20">
-        <f t="shared" ref="M107" si="99">L107*5</f>
+        <f t="shared" ref="M107" si="98">L107*5</f>
         <v>5</v>
       </c>
-      <c r="N107" s="20"/>
-      <c r="O107" s="20"/>
-      <c r="P107" s="21"/>
+      <c r="N107" s="20">
+        <v>10</v>
+      </c>
+      <c r="O107" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P107" s="45" t="s">
+        <v>632</v>
+      </c>
       <c r="Q107" s="21">
-        <f t="shared" ref="Q107" si="100">P107*N107</f>
-        <v>0</v>
+        <f t="shared" ref="Q107" si="99">P107*N107</f>
+        <v>0.38500000000000001</v>
       </c>
       <c r="R107" s="20"/>
     </row>
@@ -7415,7 +8550,7 @@
         <v>229</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G108" s="14" t="s">
         <v>359</v>
@@ -7423,12 +8558,14 @@
       <c r="H108" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="I108" s="14"/>
+      <c r="I108" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J108" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K108" s="20" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L108" s="14">
         <v>1</v>
@@ -7437,12 +8574,18 @@
         <f>L108*5</f>
         <v>5</v>
       </c>
-      <c r="N108" s="14"/>
-      <c r="O108" s="14"/>
-      <c r="P108" s="15"/>
+      <c r="N108" s="14">
+        <v>6</v>
+      </c>
+      <c r="O108" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P108" s="45" t="s">
+        <v>633</v>
+      </c>
       <c r="Q108" s="15">
         <f>P108*N108</f>
-        <v>0</v>
+        <v>83.76</v>
       </c>
       <c r="R108" s="14"/>
     </row>
@@ -7462,7 +8605,7 @@
         <v>230</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G109" s="20" t="s">
         <v>360</v>
@@ -7470,26 +8613,34 @@
       <c r="H109" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="I109" s="20"/>
+      <c r="I109" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J109" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K109" s="20" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L109" s="20">
         <v>1</v>
       </c>
       <c r="M109" s="20">
-        <f t="shared" ref="M109" si="101">L109*5</f>
+        <f t="shared" ref="M109" si="100">L109*5</f>
         <v>5</v>
       </c>
-      <c r="N109" s="20"/>
-      <c r="O109" s="20"/>
-      <c r="P109" s="21"/>
+      <c r="N109" s="20">
+        <v>10</v>
+      </c>
+      <c r="O109" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P109" s="45" t="s">
+        <v>634</v>
+      </c>
       <c r="Q109" s="21">
-        <f t="shared" ref="Q109" si="102">P109*N109</f>
-        <v>0</v>
+        <f t="shared" ref="Q109" si="101">P109*N109</f>
+        <v>2.306</v>
       </c>
       <c r="R109" s="20"/>
     </row>
@@ -7509,7 +8660,7 @@
         <v>231</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G110" s="14" t="s">
         <v>361</v>
@@ -7517,12 +8668,14 @@
       <c r="H110" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="I110" s="14"/>
+      <c r="I110" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J110" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K110" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="L110" s="14">
         <v>1</v>
@@ -7531,12 +8684,18 @@
         <f>L110*5</f>
         <v>5</v>
       </c>
-      <c r="N110" s="14"/>
-      <c r="O110" s="14"/>
-      <c r="P110" s="15"/>
+      <c r="N110" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="O110" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P110" s="45" t="s">
+        <v>635</v>
+      </c>
       <c r="Q110" s="15">
         <f>P110*N110</f>
-        <v>0</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="R110" s="14"/>
     </row>
@@ -7556,7 +8715,7 @@
         <v>232</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G111" s="20" t="s">
         <v>362</v>
@@ -7564,26 +8723,34 @@
       <c r="H111" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="I111" s="20"/>
+      <c r="I111" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J111" s="20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K111" s="20" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L111" s="20">
         <v>1</v>
       </c>
       <c r="M111" s="20">
-        <f t="shared" ref="M111" si="103">L111*5</f>
+        <f t="shared" ref="M111" si="102">L111*5</f>
         <v>5</v>
       </c>
-      <c r="N111" s="20"/>
-      <c r="O111" s="20"/>
-      <c r="P111" s="21"/>
+      <c r="N111" s="20">
+        <v>6</v>
+      </c>
+      <c r="O111" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P111" s="45" t="s">
+        <v>636</v>
+      </c>
       <c r="Q111" s="21">
-        <f t="shared" ref="Q111" si="104">P111*N111</f>
-        <v>0</v>
+        <f t="shared" ref="Q111" si="103">P111*N111</f>
+        <v>1.1958</v>
       </c>
       <c r="R111" s="20"/>
     </row>
@@ -7611,12 +8778,14 @@
       <c r="H112" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="I112" s="14"/>
+      <c r="I112" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J112" s="14" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K112" s="14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L112" s="14">
         <v>1</v>
@@ -7625,12 +8794,18 @@
         <f>L112*5</f>
         <v>5</v>
       </c>
-      <c r="N112" s="14"/>
-      <c r="O112" s="14"/>
-      <c r="P112" s="15"/>
+      <c r="N112" s="14">
+        <v>6</v>
+      </c>
+      <c r="O112" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P112" s="45" t="s">
+        <v>577</v>
+      </c>
       <c r="Q112" s="15">
         <f>P112*N112</f>
-        <v>0</v>
+        <v>1.5996000000000001</v>
       </c>
       <c r="R112" s="14"/>
     </row>
@@ -7658,26 +8833,34 @@
       <c r="H113" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="I113" s="20"/>
+      <c r="I113" s="56" t="s">
+        <v>650</v>
+      </c>
       <c r="J113" s="20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K113" s="20" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L113" s="20">
         <v>1</v>
       </c>
       <c r="M113" s="20">
-        <f t="shared" ref="M113" si="105">L113*5</f>
+        <f t="shared" ref="M113" si="104">L113*5</f>
         <v>5</v>
       </c>
-      <c r="N113" s="20"/>
-      <c r="O113" s="20"/>
-      <c r="P113" s="21"/>
+      <c r="N113" s="20">
+        <v>6</v>
+      </c>
+      <c r="O113" s="44" t="s">
+        <v>646</v>
+      </c>
+      <c r="P113" s="45" t="s">
+        <v>637</v>
+      </c>
       <c r="Q113" s="21">
-        <f t="shared" ref="Q113" si="106">P113*N113</f>
-        <v>0</v>
+        <f t="shared" ref="Q113" si="105">P113*N113</f>
+        <v>1.8540000000000001</v>
       </c>
       <c r="R113" s="20"/>
     </row>
@@ -7695,14 +8878,14 @@
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
-      <c r="N114" s="44" t="s">
+      <c r="N114" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="O114" s="45"/>
-      <c r="P114" s="45"/>
-      <c r="Q114" s="18" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
+      <c r="O114" s="48"/>
+      <c r="P114" s="48"/>
+      <c r="Q114" s="18">
+        <f>SUM(Q8:Q113)</f>
+        <v>492.32419999999985</v>
       </c>
       <c r="R114" s="1"/>
     </row>
@@ -7720,14 +8903,14 @@
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
-      <c r="N115" s="44" t="s">
+      <c r="N115" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="O115" s="45"/>
-      <c r="P115" s="45"/>
-      <c r="Q115" s="19" t="e">
+      <c r="O115" s="48"/>
+      <c r="P115" s="48"/>
+      <c r="Q115" s="19">
         <f>Q114/5</f>
-        <v>#REF!</v>
+        <v>98.464839999999967</v>
       </c>
       <c r="R115" s="1"/>
     </row>
@@ -7742,8 +8925,113 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
+    <hyperlink ref="O9" r:id="rId2"/>
+    <hyperlink ref="O10" r:id="rId3"/>
+    <hyperlink ref="O11" r:id="rId4"/>
+    <hyperlink ref="O12" r:id="rId5"/>
+    <hyperlink ref="O13" r:id="rId6"/>
+    <hyperlink ref="O14" r:id="rId7"/>
+    <hyperlink ref="O15" r:id="rId8"/>
+    <hyperlink ref="O16" r:id="rId9"/>
+    <hyperlink ref="O17" r:id="rId10"/>
+    <hyperlink ref="O18" r:id="rId11"/>
+    <hyperlink ref="O19" r:id="rId12"/>
+    <hyperlink ref="O20" r:id="rId13"/>
+    <hyperlink ref="O21" r:id="rId14"/>
+    <hyperlink ref="O22" r:id="rId15"/>
+    <hyperlink ref="O23" r:id="rId16"/>
+    <hyperlink ref="O24" r:id="rId17"/>
+    <hyperlink ref="O25" r:id="rId18"/>
+    <hyperlink ref="O27" r:id="rId19"/>
+    <hyperlink ref="O28" r:id="rId20"/>
+    <hyperlink ref="O29" r:id="rId21"/>
+    <hyperlink ref="O30" r:id="rId22"/>
+    <hyperlink ref="O31" r:id="rId23"/>
+    <hyperlink ref="O32" r:id="rId24"/>
+    <hyperlink ref="O33" r:id="rId25"/>
+    <hyperlink ref="O34" r:id="rId26"/>
+    <hyperlink ref="O35" r:id="rId27"/>
+    <hyperlink ref="O36" r:id="rId28"/>
+    <hyperlink ref="O37" r:id="rId29"/>
+    <hyperlink ref="O38" r:id="rId30"/>
+    <hyperlink ref="O39" r:id="rId31"/>
+    <hyperlink ref="O40" r:id="rId32"/>
+    <hyperlink ref="O41" r:id="rId33"/>
+    <hyperlink ref="O42" r:id="rId34"/>
+    <hyperlink ref="O43" r:id="rId35"/>
+    <hyperlink ref="O44" r:id="rId36"/>
+    <hyperlink ref="O45" r:id="rId37"/>
+    <hyperlink ref="O46" r:id="rId38"/>
+    <hyperlink ref="O47" r:id="rId39"/>
+    <hyperlink ref="O48" r:id="rId40"/>
+    <hyperlink ref="O49" r:id="rId41"/>
+    <hyperlink ref="O50" r:id="rId42"/>
+    <hyperlink ref="O51" r:id="rId43"/>
+    <hyperlink ref="O52" r:id="rId44"/>
+    <hyperlink ref="O53" r:id="rId45"/>
+    <hyperlink ref="O54" r:id="rId46"/>
+    <hyperlink ref="O55" r:id="rId47"/>
+    <hyperlink ref="O56" r:id="rId48"/>
+    <hyperlink ref="O57" r:id="rId49"/>
+    <hyperlink ref="O58" r:id="rId50"/>
+    <hyperlink ref="O59" r:id="rId51"/>
+    <hyperlink ref="O60" r:id="rId52"/>
+    <hyperlink ref="O61" r:id="rId53"/>
+    <hyperlink ref="O62" r:id="rId54"/>
+    <hyperlink ref="O63" r:id="rId55"/>
+    <hyperlink ref="O64" r:id="rId56"/>
+    <hyperlink ref="O65" r:id="rId57"/>
+    <hyperlink ref="O66" r:id="rId58"/>
+    <hyperlink ref="O67" r:id="rId59"/>
+    <hyperlink ref="O68" r:id="rId60"/>
+    <hyperlink ref="O69" r:id="rId61"/>
+    <hyperlink ref="O70" r:id="rId62"/>
+    <hyperlink ref="O71" r:id="rId63"/>
+    <hyperlink ref="O72" r:id="rId64"/>
+    <hyperlink ref="O73" r:id="rId65"/>
+    <hyperlink ref="O74" r:id="rId66"/>
+    <hyperlink ref="O75" r:id="rId67"/>
+    <hyperlink ref="O76" r:id="rId68"/>
+    <hyperlink ref="O77" r:id="rId69"/>
+    <hyperlink ref="O78" r:id="rId70"/>
+    <hyperlink ref="O79" r:id="rId71"/>
+    <hyperlink ref="O80" r:id="rId72"/>
+    <hyperlink ref="O81" r:id="rId73"/>
+    <hyperlink ref="O82" r:id="rId74"/>
+    <hyperlink ref="O83" r:id="rId75"/>
+    <hyperlink ref="O84" r:id="rId76"/>
+    <hyperlink ref="O85" r:id="rId77"/>
+    <hyperlink ref="O86" r:id="rId78"/>
+    <hyperlink ref="O88" r:id="rId79"/>
+    <hyperlink ref="O89" r:id="rId80"/>
+    <hyperlink ref="O90" r:id="rId81"/>
+    <hyperlink ref="O91" r:id="rId82"/>
+    <hyperlink ref="O92" r:id="rId83"/>
+    <hyperlink ref="O93" r:id="rId84"/>
+    <hyperlink ref="O94" r:id="rId85"/>
+    <hyperlink ref="O95" r:id="rId86"/>
+    <hyperlink ref="O96" r:id="rId87"/>
+    <hyperlink ref="O97" r:id="rId88"/>
+    <hyperlink ref="O98" r:id="rId89"/>
+    <hyperlink ref="O100" r:id="rId90"/>
+    <hyperlink ref="O101" r:id="rId91"/>
+    <hyperlink ref="O102" r:id="rId92"/>
+    <hyperlink ref="O104" r:id="rId93"/>
+    <hyperlink ref="O105" r:id="rId94"/>
+    <hyperlink ref="O108" r:id="rId95"/>
+    <hyperlink ref="O109" r:id="rId96"/>
+    <hyperlink ref="O110" r:id="rId97"/>
+    <hyperlink ref="O111" r:id="rId98"/>
+    <hyperlink ref="O112" r:id="rId99"/>
+    <hyperlink ref="O113" r:id="rId100"/>
+    <hyperlink ref="O26" r:id="rId101"/>
+    <hyperlink ref="O87" r:id="rId102"/>
+    <hyperlink ref="O103" r:id="rId103"/>
+    <hyperlink ref="O106" r:id="rId104"/>
+    <hyperlink ref="O107" r:id="rId105"/>
+    <hyperlink ref="O99" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId107"/>
 </worksheet>
 </file>